--- a/data/acompanhamento/trilhas/Capacitação Avançada 2025.xlsx
+++ b/data/acompanhamento/trilhas/Capacitação Avançada 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\Tiago\Feadev\Projetos\Mae DEV\Repositorio\Sistema_MAE\data\trilhas_atualizadas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\Tiago\Feadev\Projetos\Mae DEV\Repositorio\Sistema_MAE\data\acompanhamento\trilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB6A5CC-D6E3-48CE-8689-681D96FEDAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C146F1E6-D7EF-4A28-A656-27C4AB4AD06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
   <si>
     <t>Trilha</t>
   </si>
@@ -56,15 +56,6 @@
     <t>obrigatoriedade_curso</t>
   </si>
   <si>
-    <t>4 hr</t>
-  </si>
-  <si>
-    <t>3 hr</t>
-  </si>
-  <si>
-    <t>2 hr</t>
-  </si>
-  <si>
     <t>Introduction to Object-Oriented Programming in Python</t>
   </si>
   <si>
@@ -132,6 +123,9 @@
   </si>
   <si>
     <t>Capacitação Avançada 2025</t>
+  </si>
+  <si>
+    <t>xp_curso</t>
   </si>
 </sst>
 </file>
@@ -501,19 +495,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -524,455 +518,524 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1500</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>3950</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>3950</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>2800</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>2250</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>2500</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>2250</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
         <v>9</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>4500</v>
+      </c>
+      <c r="E9">
+        <v>7</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>3100</v>
+      </c>
+      <c r="E10">
+        <v>8</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>3300</v>
+      </c>
+      <c r="E11">
+        <v>9</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <v>4700</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>4050</v>
+      </c>
+      <c r="E13">
+        <v>11</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>4700</v>
+      </c>
+      <c r="E14">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15">
+        <v>4850</v>
+      </c>
+      <c r="E15">
+        <v>13</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16">
+        <v>3950</v>
+      </c>
+      <c r="E16">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <v>3250</v>
+      </c>
+      <c r="E17">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18">
+        <v>4250</v>
+      </c>
+      <c r="E18">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19">
+        <v>4150</v>
+      </c>
+      <c r="E19">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>3500</v>
+      </c>
+      <c r="E20">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21">
+        <v>4550</v>
+      </c>
+      <c r="E21">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8">
-        <v>6</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9">
-        <v>7</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10">
-        <v>8</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11">
-        <v>9</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22">
+        <v>4</v>
+      </c>
+      <c r="D22">
+        <v>4500</v>
+      </c>
+      <c r="E22">
         <v>20</v>
       </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12">
-        <v>10</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23">
+        <v>4200</v>
+      </c>
+      <c r="E23">
         <v>21</v>
       </c>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13">
-        <v>11</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14">
-        <v>12</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15">
-        <v>13</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16">
-        <v>14</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17">
-        <v>15</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18">
-        <v>16</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19">
-        <v>17</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20">
-        <v>18</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21">
-        <v>19</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22">
-        <v>20</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23">
-        <v>21</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="G23">
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="H23">
         <v>1</v>
       </c>
     </row>
